--- a/public/templates/000_pm_suite/01_프로젝트 관리/04_비용관리/프로젝트명_비용관리_V1.0_20230530.xlsx
+++ b/public/templates/000_pm_suite/01_프로젝트 관리/04_비용관리/프로젝트명_비용관리_V1.0_20230530.xlsx
@@ -547,7 +547,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>[PM-13] SyncGuard AI 프로젝트 비용관리 및 대금 청구·외주 집행 대장 — 주식회사 한빛글로벌 SyncGuard AI 시스템 구축</t>
+          <t>[PM-13] SyncFlow AI 프로젝트 비용관리 및 대금 청구·외주 집행 대장 — 주식회사 한빛글로벌 SyncFlow AI 시스템 구축</t>
         </is>
       </c>
     </row>
